--- a/kortdata/PU_BYA.xlsx
+++ b/kortdata/PU_BYA.xlsx
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Klass A:s undre gräns i CSV (500) stämmer inte med trycket (0). CSV:n ändrades efter att tryckfilen skapades; trycket är facit. Se KORRIGERINGAR i skriptet.</t>
+          <t>Klass A:s undre gräns i CSV (500) stämmer inte med trycket (0). CSV:n ändrades efter att tryckfilen skapades; trycket är facit. Se KORRIGERINGAR i skriptet. Bekräftat av användaren: gränsen följer korten.</t>
         </is>
       </c>
     </row>
